--- a/e2e-screenshots/accessory-return-returns-page/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/accessory-return-returns-page/downloaded-sales-report.xlsx
@@ -320,7 +320,7 @@
     <t>Carriage costed from</t>
   </si>
   <si>
-    <t>2026-08-07</t>
+    <t>2026-08-08</t>
   </si>
   <si>
     <t>Uncosted (pre-tracking) returns</t>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>46241.5</v>
+        <v>46242.5</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="8">
-        <v>46241.5</v>
+        <v>46242.5</v>
       </c>
       <c r="H2" s="11">
         <v>26.97</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>46241.5</v>
+        <v>46242.5</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>56</v>
@@ -1413,7 +1413,7 @@
         <f>V2-Y2</f>
       </c>
       <c r="AA2" s="8">
-        <v>46241.5</v>
+        <v>46242.5</v>
       </c>
       <c r="AB2" s="9" t="s">
         <v>58</v>
@@ -44810,7 +44810,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>46241.5</v>
+        <v>46242.5</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>13</v>

--- a/e2e-screenshots/accessory-return-returns-page/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/accessory-return-returns-page/downloaded-sales-report.xlsx
@@ -320,7 +320,7 @@
     <t>Carriage costed from</t>
   </si>
   <si>
-    <t>2026-08-08</t>
+    <t>2026-08-11</t>
   </si>
   <si>
     <t>Uncosted (pre-tracking) returns</t>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>46242.5</v>
+        <v>46245.5</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="8">
-        <v>46242.5</v>
+        <v>46245.5</v>
       </c>
       <c r="H2" s="11">
         <v>26.97</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>46242.5</v>
+        <v>46245.5</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>56</v>
@@ -1413,7 +1413,7 @@
         <f>V2-Y2</f>
       </c>
       <c r="AA2" s="8">
-        <v>46242.5</v>
+        <v>46245.5</v>
       </c>
       <c r="AB2" s="9" t="s">
         <v>58</v>
@@ -44810,7 +44810,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>46242.5</v>
+        <v>46245.5</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>13</v>
